--- a/5_Judgemental_Forecasts_Derivations_Analysis/0_Main/AR2/0_EDA_Tables/Forecast_Series_h6.xlsx
+++ b/5_Judgemental_Forecasts_Derivations_Analysis/0_Main/AR2/0_EDA_Tables/Forecast_Series_h6.xlsx
@@ -459,22 +459,22 @@
         <v>0.25</v>
       </c>
       <c r="D2">
-        <v>0.5428545301107226</v>
+        <v>0.4507836700716622</v>
       </c>
       <c r="E2">
         <v>0.2404915850527668</v>
       </c>
       <c r="F2">
-        <v>0.5333461151634894</v>
+        <v>0.4412752551244291</v>
       </c>
       <c r="G2">
-        <v>-0.2928545301107226</v>
+        <v>-0.2007836700716622</v>
       </c>
       <c r="H2">
-        <v>0.2928545301107226</v>
+        <v>0.2007836700716622</v>
       </c>
       <c r="I2">
-        <v>0.2266218760787939</v>
+        <v>0.1368876483039378</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
@@ -497,31 +497,31 @@
         <v>0.25</v>
       </c>
       <c r="D3">
-        <v>0.4739989517431839</v>
+        <v>-3.487028714824694</v>
       </c>
       <c r="E3">
         <v>-0.1147970816233392</v>
       </c>
       <c r="F3">
-        <v>0.1092018701198447</v>
+        <v>-3.851825796448033</v>
       </c>
       <c r="G3">
-        <v>-0.2239989517431839</v>
+        <v>3.737028714824694</v>
       </c>
       <c r="H3">
-        <v>-0.005595211503494457</v>
+        <v>3.737028714824694</v>
       </c>
       <c r="I3">
-        <v>-0.001253321511564163</v>
+        <v>14.82338359623329</v>
       </c>
       <c r="J3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -535,31 +535,31 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="D4">
-        <v>0.4823252873721797</v>
+        <v>0.210717324786206</v>
       </c>
       <c r="E4">
         <v>0.5818677821224053</v>
       </c>
       <c r="F4">
-        <v>0.6641930694945793</v>
+        <v>0.3925851069086056</v>
       </c>
       <c r="G4">
-        <v>-0.08232528737217404</v>
+        <v>0.1892826752137997</v>
       </c>
       <c r="H4">
-        <v>0.08232528737217404</v>
+        <v>-0.1892826752137997</v>
       </c>
       <c r="I4">
-        <v>0.1025823176925842</v>
+        <v>-0.1844470497056057</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
       </c>
       <c r="K4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -573,22 +573,22 @@
         <v>0.6</v>
       </c>
       <c r="D5">
-        <v>0.5066744399319</v>
+        <v>0.3342301838978883</v>
       </c>
       <c r="E5">
         <v>1.192512792889843</v>
       </c>
       <c r="F5">
-        <v>1.099187232821743</v>
+        <v>0.9267429767877318</v>
       </c>
       <c r="G5">
-        <v>0.0933255600681</v>
+        <v>0.2657698161021117</v>
       </c>
       <c r="H5">
-        <v>-0.0933255600681</v>
+        <v>-0.2657698161021116</v>
       </c>
       <c r="I5">
-        <v>-0.213874188407613</v>
+        <v>-0.5632342161805481</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
@@ -611,25 +611,25 @@
         <v>0.5</v>
       </c>
       <c r="D6">
-        <v>0.4950019970017591</v>
+        <v>0.2802649951984016</v>
       </c>
       <c r="E6">
         <v>0.1162427487728631</v>
       </c>
       <c r="F6">
-        <v>0.1112447457746222</v>
+        <v>-0.1034922560287353</v>
       </c>
       <c r="G6">
-        <v>0.00499800299824088</v>
+        <v>0.2197350048015984</v>
       </c>
       <c r="H6">
-        <v>-0.00499800299824088</v>
+        <v>-0.01275049274412782</v>
       </c>
       <c r="I6">
-        <v>-0.001136983179810638</v>
+        <v>-0.002801729584353671</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
@@ -649,22 +649,22 @@
         <v>0.4999999999999858</v>
       </c>
       <c r="D7">
-        <v>0.4842631012989744</v>
+        <v>0.2204108026459904</v>
       </c>
       <c r="E7">
         <v>-0.1996974281391924</v>
       </c>
       <c r="F7">
-        <v>-0.2154343268402039</v>
+        <v>-0.4792866254931878</v>
       </c>
       <c r="G7">
-        <v>0.01573689870101141</v>
+        <v>0.2795891973539954</v>
       </c>
       <c r="H7">
-        <v>0.01573689870101141</v>
+        <v>0.2795891973539954</v>
       </c>
       <c r="I7">
-        <v>0.006532886375683854</v>
+        <v>0.1898366065712394</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
@@ -687,22 +687,22 @@
         <v>0.5200000000000102</v>
       </c>
       <c r="D8">
-        <v>0.4884041605467166</v>
+        <v>0.3242276085240325</v>
       </c>
       <c r="E8">
         <v>0.2513073288242555</v>
       </c>
       <c r="F8">
-        <v>0.2197114893709619</v>
+        <v>0.0555349373482778</v>
       </c>
       <c r="G8">
-        <v>0.03159583945329364</v>
+        <v>0.1957723914759777</v>
       </c>
       <c r="H8">
-        <v>-0.03159583945329364</v>
+        <v>-0.1957723914759777</v>
       </c>
       <c r="I8">
-        <v>-0.01488223495917619</v>
+        <v>-0.06007124425450536</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
@@ -725,28 +725,28 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="D9">
-        <v>0.4780923718803366</v>
+        <v>0.3370198469658729</v>
       </c>
       <c r="E9">
         <v>-0.0269234262875761</v>
       </c>
       <c r="F9">
-        <v>0.05116894559275481</v>
+        <v>-0.08990357932170889</v>
       </c>
       <c r="G9">
-        <v>-0.07809237188033091</v>
+        <v>0.06298015303413279</v>
       </c>
       <c r="H9">
-        <v>0.02424551930517871</v>
+        <v>0.06298015303413279</v>
       </c>
       <c r="I9">
-        <v>0.001893390110011758</v>
+        <v>0.007357782691792259</v>
       </c>
       <c r="J9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="b">
         <v>1</v>
@@ -763,22 +763,22 @@
         <v>0.4799999999999898</v>
       </c>
       <c r="D10">
-        <v>0.4794792177817959</v>
+        <v>0.3501398362063016</v>
       </c>
       <c r="E10">
         <v>-0.126966924700923</v>
       </c>
       <c r="F10">
-        <v>-0.1274877069191169</v>
+        <v>-0.2568270884946112</v>
       </c>
       <c r="G10">
-        <v>0.0005207822181939048</v>
+        <v>0.1298601637936882</v>
       </c>
       <c r="H10">
-        <v>0.0005207822181939048</v>
+        <v>0.1298601637936882</v>
       </c>
       <c r="I10">
-        <v>0.0001325154474847989</v>
+        <v>0.04983955341660901</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
@@ -801,31 +801,31 @@
         <v>0.4499999999999886</v>
       </c>
       <c r="D11">
-        <v>0.4806792685643219</v>
+        <v>0.3932291613384508</v>
       </c>
       <c r="E11">
         <v>0.4326764833261072</v>
       </c>
       <c r="F11">
-        <v>0.4633557518904405</v>
+        <v>0.3759056446645694</v>
       </c>
       <c r="G11">
-        <v>-0.03067926856433334</v>
+        <v>0.05677083866153776</v>
       </c>
       <c r="H11">
-        <v>0.03067926856433334</v>
+        <v>-0.05677083866153776</v>
       </c>
       <c r="I11">
-        <v>0.02748961358650837</v>
+        <v>-0.04590388553276156</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -839,22 +839,22 @@
         <v>0.4999999999999858</v>
       </c>
       <c r="D12">
-        <v>0.4877996875454527</v>
+        <v>0.4030874550409006</v>
       </c>
       <c r="E12">
         <v>0.4158406583130553</v>
       </c>
       <c r="F12">
-        <v>0.4036403458585223</v>
+        <v>0.3189281133539701</v>
       </c>
       <c r="G12">
-        <v>0.01220031245453307</v>
+        <v>0.09691254495908519</v>
       </c>
       <c r="H12">
-        <v>-0.01220031245453307</v>
+        <v>-0.09691254495908519</v>
       </c>
       <c r="I12">
-        <v>-0.009997924301447775</v>
+        <v>-0.07120831161871242</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
@@ -877,31 +877,31 @@
         <v>0.4490000000000123</v>
       </c>
       <c r="D13">
-        <v>0.4864028713123654</v>
+        <v>0.3735474909819056</v>
       </c>
       <c r="E13">
         <v>0.4210044792833259</v>
       </c>
       <c r="F13">
-        <v>0.4584073505956791</v>
+        <v>0.3455519702652192</v>
       </c>
       <c r="G13">
-        <v>-0.03740287131235315</v>
+        <v>0.07545250901810668</v>
       </c>
       <c r="H13">
-        <v>0.03740287131235315</v>
+        <v>-0.07545250901810668</v>
       </c>
       <c r="I13">
-        <v>0.03289252750352542</v>
+        <v>-0.05783860742244944</v>
       </c>
       <c r="J13" t="b">
         <v>1</v>
       </c>
       <c r="K13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -915,22 +915,22 @@
         <v>0.2999999999999829</v>
       </c>
       <c r="D14">
-        <v>0.4884335660315953</v>
+        <v>0.3506438818109137</v>
       </c>
       <c r="E14">
         <v>2.521807318894689</v>
       </c>
       <c r="F14">
-        <v>2.710240884926301</v>
+        <v>2.57245120070562</v>
       </c>
       <c r="G14">
-        <v>-0.1884335660316124</v>
+        <v>-0.05064388181093082</v>
       </c>
       <c r="H14">
-        <v>0.1884335660316125</v>
+        <v>0.05064388181093094</v>
       </c>
       <c r="I14">
-        <v>0.9858935006952825</v>
+        <v>0.2579930263809658</v>
       </c>
       <c r="J14" t="b">
         <v>1</v>
@@ -953,22 +953,22 @@
         <v>0.3</v>
       </c>
       <c r="D15">
-        <v>0.484149358105795</v>
+        <v>0.3227261879073491</v>
       </c>
       <c r="E15">
         <v>9.990957649752</v>
       </c>
       <c r="F15">
-        <v>10.17510700785779</v>
+        <v>10.01368383765935</v>
       </c>
       <c r="G15">
-        <v>-0.184149358105795</v>
+        <v>-0.02272618790734909</v>
       </c>
       <c r="H15">
-        <v>0.1841493581057936</v>
+        <v>0.02272618790734882</v>
       </c>
       <c r="I15">
-        <v>3.713567862218781</v>
+        <v>0.4546292414620581</v>
       </c>
       <c r="J15" t="b">
         <v>1</v>
@@ -991,31 +991,31 @@
         <v>0.3500000000000085</v>
       </c>
       <c r="D16">
-        <v>0.4817408797410174</v>
+        <v>0.2984907630999368</v>
       </c>
       <c r="E16">
         <v>-8.130304150385461</v>
       </c>
       <c r="F16">
-        <v>-7.998563270644452</v>
+        <v>-8.181813387285533</v>
       </c>
       <c r="G16">
-        <v>-0.1317408797410089</v>
+        <v>0.05150923690007175</v>
       </c>
       <c r="H16">
-        <v>-0.1317408797410087</v>
+        <v>0.05150923690007225</v>
       </c>
       <c r="I16">
-        <v>-2.124831183272569</v>
+        <v>0.8402247265897245</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
       </c>
       <c r="K16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1029,31 +1029,31 @@
         <v>0.3</v>
       </c>
       <c r="D17">
-        <v>0.4819766123135046</v>
+        <v>0.3181327414019882</v>
       </c>
       <c r="E17">
         <v>-0.04063260340632052</v>
       </c>
       <c r="F17">
-        <v>0.1413440089071841</v>
+        <v>-0.02249986200433229</v>
       </c>
       <c r="G17">
-        <v>-0.1819766123135046</v>
+        <v>-0.01813274140198823</v>
       </c>
       <c r="H17">
-        <v>0.1007114055008635</v>
+        <v>-0.01813274140198823</v>
       </c>
       <c r="I17">
-        <v>0.0183271203943788</v>
+        <v>-0.001144764669361334</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="b">
         <v>1</v>
       </c>
       <c r="L17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1067,31 +1067,31 @@
         <v>0.3490000000000038</v>
       </c>
       <c r="D18">
-        <v>0.4774302065376628</v>
+        <v>0.2966710407067586</v>
       </c>
       <c r="E18">
         <v>2.155937868393076</v>
       </c>
       <c r="F18">
-        <v>2.284368074930735</v>
+        <v>2.10360890909983</v>
       </c>
       <c r="G18">
-        <v>-0.128430206537659</v>
+        <v>0.05232895929324521</v>
       </c>
       <c r="H18">
-        <v>0.1284302065376588</v>
+        <v>-0.05232895929324544</v>
       </c>
       <c r="I18">
-        <v>0.5702694093914706</v>
+        <v>-0.2228976499271011</v>
       </c>
       <c r="J18" t="b">
         <v>1</v>
       </c>
       <c r="K18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1105,31 +1105,31 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="D19">
-        <v>0.474780603671684</v>
+        <v>0.2898675503809542</v>
       </c>
       <c r="E19">
         <v>-1.233092118130252</v>
       </c>
       <c r="F19">
-        <v>-1.158311514458574</v>
+        <v>-1.343224567749304</v>
       </c>
       <c r="G19">
-        <v>-0.07478060367167833</v>
+        <v>0.1101324496190515</v>
       </c>
       <c r="H19">
-        <v>-0.07478060367167827</v>
+        <v>0.1101324496190514</v>
       </c>
       <c r="I19">
-        <v>-0.1788306072676369</v>
+        <v>0.2837360676103517</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
       </c>
       <c r="K19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1143,31 +1143,31 @@
         <v>0.3821739059768845</v>
       </c>
       <c r="D20">
-        <v>0.473275785632121</v>
+        <v>0.2789933017497698</v>
       </c>
       <c r="E20">
         <v>-1.312092390567575</v>
       </c>
       <c r="F20">
-        <v>-1.220990510912338</v>
+        <v>-1.415272994794689</v>
       </c>
       <c r="G20">
-        <v>-0.09110187965523653</v>
+        <v>0.1031806042271147</v>
       </c>
       <c r="H20">
-        <v>-0.09110187965523653</v>
+        <v>0.1031806042271146</v>
       </c>
       <c r="I20">
-        <v>-0.2307686136473603</v>
+        <v>0.2814112084097955</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
       </c>
       <c r="K20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1181,31 +1181,31 @@
         <v>0.4</v>
       </c>
       <c r="D21">
-        <v>0.4557352188277789</v>
+        <v>0.1681088150593795</v>
       </c>
       <c r="E21">
         <v>0.7471896406117955</v>
       </c>
       <c r="F21">
-        <v>0.8029248594395744</v>
+        <v>0.5152984556711749</v>
       </c>
       <c r="G21">
-        <v>-0.05573521882777888</v>
+        <v>0.2318911849406205</v>
       </c>
       <c r="H21">
-        <v>0.05573521882777888</v>
+        <v>-0.2318911849406206</v>
       </c>
       <c r="I21">
-        <v>0.08639597086847617</v>
+        <v>-0.2927598606204863</v>
       </c>
       <c r="J21" t="b">
         <v>1</v>
       </c>
       <c r="K21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -1219,31 +1219,31 @@
         <v>0.3892477923702176</v>
       </c>
       <c r="D22">
-        <v>0.3548656949390632</v>
+        <v>-1.93210807464721</v>
       </c>
       <c r="E22">
         <v>0.153842895948372</v>
       </c>
       <c r="F22">
-        <v>0.1194607985172176</v>
+        <v>-2.167512971069056</v>
       </c>
       <c r="G22">
-        <v>0.03438209743115439</v>
+        <v>2.321355867017428</v>
       </c>
       <c r="H22">
-        <v>-0.03438209743115439</v>
+        <v>2.013670075120684</v>
       </c>
       <c r="I22">
-        <v>-0.009396754251410356</v>
+        <v>4.674444843118823</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="b">
         <v>0</v>
       </c>
       <c r="L22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1257,31 +1257,31 @@
         <v>0.4396079355184761</v>
       </c>
       <c r="D23">
-        <v>0.4414245437697561</v>
+        <v>-0.02270422417448745</v>
       </c>
       <c r="E23">
         <v>0.2998780799059883</v>
       </c>
       <c r="F23">
-        <v>0.3016946881572683</v>
+        <v>-0.1624340797869752</v>
       </c>
       <c r="G23">
-        <v>-0.001816608251279994</v>
+        <v>0.4623121596929636</v>
       </c>
       <c r="H23">
-        <v>0.001816608251279994</v>
+        <v>-0.1374440001190131</v>
       </c>
       <c r="I23">
-        <v>0.001092822054209061</v>
+        <v>-0.06354203253186086</v>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -1295,28 +1295,28 @@
         <v>0.4329</v>
       </c>
       <c r="D24">
-        <v>0.4523860776188074</v>
+        <v>0.2292596098352697</v>
       </c>
       <c r="E24">
         <v>0.03275110738878939</v>
       </c>
       <c r="F24">
-        <v>0.05223718500759678</v>
+        <v>-0.1708892827759409</v>
       </c>
       <c r="G24">
-        <v>-0.01948607761880738</v>
+        <v>0.2036403901647303</v>
       </c>
       <c r="H24">
-        <v>0.01948607761880738</v>
+        <v>0.1381381753871515</v>
       </c>
       <c r="I24">
-        <v>0.001656088462325878</v>
+        <v>0.02813051193248349</v>
       </c>
       <c r="J24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" t="b">
         <v>1</v>
@@ -1333,31 +1333,31 @@
         <v>0.4251122424301368</v>
       </c>
       <c r="D25">
-        <v>0.4458480184709741</v>
+        <v>0.2970735349662799</v>
       </c>
       <c r="E25">
         <v>0.8604183459774174</v>
       </c>
       <c r="F25">
-        <v>0.8811541220182547</v>
+        <v>0.7323796385135606</v>
       </c>
       <c r="G25">
-        <v>-0.02073577604083732</v>
+        <v>0.1280387074638569</v>
       </c>
       <c r="H25">
-        <v>0.02073577604083732</v>
+        <v>-0.1280387074638568</v>
       </c>
       <c r="I25">
-        <v>0.03611285665524655</v>
+        <v>-0.2039397951852612</v>
       </c>
       <c r="J25" t="b">
         <v>1</v>
       </c>
       <c r="K25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -1371,22 +1371,22 @@
         <v>0.26</v>
       </c>
       <c r="D26">
-        <v>0.4534345630322582</v>
+        <v>0.3634760761829015</v>
       </c>
       <c r="E26">
         <v>0.5952267436446591</v>
       </c>
       <c r="F26">
-        <v>0.7886613066769173</v>
+        <v>0.6987028198275607</v>
       </c>
       <c r="G26">
-        <v>-0.1934345630322582</v>
+        <v>-0.1034760761829015</v>
       </c>
       <c r="H26">
-        <v>0.1934345630322581</v>
+        <v>0.1034760761829016</v>
       </c>
       <c r="I26">
-        <v>0.2676917802995178</v>
+        <v>0.13389075408516</v>
       </c>
       <c r="J26" t="b">
         <v>1</v>
@@ -1409,22 +1409,22 @@
         <v>0.32</v>
       </c>
       <c r="D27">
-        <v>0.4609549054534036</v>
+        <v>0.3807131794959351</v>
       </c>
       <c r="E27">
         <v>0.3014402375649629</v>
       </c>
       <c r="F27">
-        <v>0.4423951430183665</v>
+        <v>0.3621534170608979</v>
       </c>
       <c r="G27">
-        <v>-0.1409549054534036</v>
+        <v>-0.06071317949593508</v>
       </c>
       <c r="H27">
-        <v>0.1409549054534036</v>
+        <v>0.06071317949593508</v>
       </c>
       <c r="I27">
-        <v>0.1048472457430197</v>
+        <v>0.04028888066566344</v>
       </c>
       <c r="J27" t="b">
         <v>1</v>
@@ -1447,22 +1447,22 @@
         <v>0.4835366100679694</v>
       </c>
       <c r="D28">
-        <v>0.4602503916373911</v>
+        <v>0.3872693173527261</v>
       </c>
       <c r="E28">
         <v>0.6131542380653776</v>
       </c>
       <c r="F28">
-        <v>0.5898680196347993</v>
+        <v>0.5168869453501342</v>
       </c>
       <c r="G28">
-        <v>0.02328621843057826</v>
+        <v>0.09626729271524331</v>
       </c>
       <c r="H28">
-        <v>-0.02328621843057832</v>
+        <v>-0.09626729271524337</v>
       </c>
       <c r="I28">
-        <v>-0.02801383906965382</v>
+        <v>-0.1087860053841411</v>
       </c>
       <c r="J28" t="b">
         <v>1</v>
@@ -1485,31 +1485,31 @@
         <v>0.42</v>
       </c>
       <c r="D29">
-        <v>0.4592809324058603</v>
+        <v>0.3937214059541168</v>
       </c>
       <c r="E29">
         <v>0.7070636170015632</v>
       </c>
       <c r="F29">
-        <v>0.7463445494074235</v>
+        <v>0.68078502295568</v>
       </c>
       <c r="G29">
-        <v>-0.03928093240586034</v>
+        <v>0.02627859404588317</v>
       </c>
       <c r="H29">
-        <v>0.03928093240586028</v>
+        <v>-0.02627859404588317</v>
       </c>
       <c r="I29">
-        <v>0.05709122794283678</v>
+        <v>-0.03647071100656746</v>
       </c>
       <c r="J29" t="b">
         <v>1</v>
       </c>
       <c r="K29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -1523,22 +1523,22 @@
         <v>0.51</v>
       </c>
       <c r="D30">
-        <v>0.4609550276426879</v>
+        <v>0.3674789505182796</v>
       </c>
       <c r="E30">
         <v>0.2964041604754924</v>
       </c>
       <c r="F30">
-        <v>0.2473591881181803</v>
+        <v>0.153883110993772</v>
       </c>
       <c r="G30">
-        <v>0.04904497235731209</v>
+        <v>0.1425210494817204</v>
       </c>
       <c r="H30">
-        <v>-0.04904497235731209</v>
+        <v>-0.1425210494817204</v>
       </c>
       <c r="I30">
-        <v>-0.02666885840069614</v>
+        <v>-0.0641754144980599</v>
       </c>
       <c r="J30" t="b">
         <v>1</v>
@@ -1561,31 +1561,31 @@
         <v>0.3657167307479057</v>
       </c>
       <c r="D31">
-        <v>0.4604305063334215</v>
+        <v>0.3564612002996471</v>
       </c>
       <c r="E31">
         <v>0.4324787717588673</v>
       </c>
       <c r="F31">
-        <v>0.527192547344383</v>
+        <v>0.4232232413106087</v>
       </c>
       <c r="G31">
-        <v>-0.09471377558551575</v>
+        <v>0.009255530448258609</v>
       </c>
       <c r="H31">
-        <v>0.09471377558551575</v>
+        <v>-0.009255530448258609</v>
       </c>
       <c r="I31">
-        <v>0.09089409395340112</v>
+        <v>-0.007919976036600718</v>
       </c>
       <c r="J31" t="b">
         <v>1</v>
       </c>
       <c r="K31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -1599,22 +1599,22 @@
         <v>0.2881898502275533</v>
       </c>
       <c r="D32">
-        <v>0.4570941208289251</v>
+        <v>0.3341572202646768</v>
       </c>
       <c r="E32">
         <v>0.1829770333935032</v>
       </c>
       <c r="F32">
-        <v>0.351881303994875</v>
+        <v>0.2289444034306267</v>
       </c>
       <c r="G32">
-        <v>-0.1689042706013718</v>
+        <v>-0.04596737003712353</v>
       </c>
       <c r="H32">
-        <v>0.1689042706013718</v>
+        <v>0.04596737003712353</v>
       </c>
       <c r="I32">
-        <v>0.09033985735164644</v>
+        <v>0.01893494511271838</v>
       </c>
       <c r="J32" t="b">
         <v>1</v>
@@ -1637,31 +1637,31 @@
         <v>0.33</v>
       </c>
       <c r="D33">
-        <v>0.4529512402202359</v>
+        <v>0.3112829433524077</v>
       </c>
       <c r="E33">
         <v>0.5306497229122814</v>
       </c>
       <c r="F33">
-        <v>0.6536009631325173</v>
+        <v>0.511932666264689</v>
       </c>
       <c r="G33">
-        <v>-0.1229512402202359</v>
+        <v>0.01871705664759232</v>
       </c>
       <c r="H33">
-        <v>0.1229512402202358</v>
+        <v>-0.01871705664759238</v>
       </c>
       <c r="I33">
-        <v>0.1456050905808731</v>
+        <v>-0.01951407363800756</v>
       </c>
       <c r="J33" t="b">
         <v>1</v>
       </c>
       <c r="K33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -1675,31 +1675,31 @@
         <v>0.3317631665228618</v>
       </c>
       <c r="D34">
-        <v>0.4535054638035673</v>
+        <v>0.2938538434164454</v>
       </c>
       <c r="E34">
         <v>-0.07991706325214298</v>
       </c>
       <c r="F34">
-        <v>0.04182523402856253</v>
+        <v>-0.1178263863585594</v>
       </c>
       <c r="G34">
-        <v>-0.1217422972807055</v>
+        <v>0.03790932310641643</v>
       </c>
       <c r="H34">
-        <v>-0.03809182922358045</v>
+        <v>0.03790932310641643</v>
       </c>
       <c r="I34">
-        <v>-0.004637386797302997</v>
+        <v>0.007496320323469492</v>
       </c>
       <c r="J34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -1713,31 +1713,31 @@
         <v>0.3</v>
       </c>
       <c r="D35">
-        <v>0.4518087430802991</v>
+        <v>0.2753750686291025</v>
       </c>
       <c r="E35">
         <v>0.5766911554241068</v>
       </c>
       <c r="F35">
-        <v>0.7284998985044058</v>
+        <v>0.5520662240532093</v>
       </c>
       <c r="G35">
-        <v>-0.1518087430802991</v>
+        <v>0.0246249313708975</v>
       </c>
       <c r="H35">
-        <v>0.151808743080299</v>
+        <v>-0.0246249313708975</v>
       </c>
       <c r="I35">
-        <v>0.1981394133765383</v>
+        <v>-0.02779557300402302</v>
       </c>
       <c r="J35" t="b">
         <v>1</v>
       </c>
       <c r="K35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -1751,31 +1751,31 @@
         <v>0.3087982760018804</v>
       </c>
       <c r="D36">
-        <v>0.4489832632463832</v>
+        <v>0.2743085116504074</v>
       </c>
       <c r="E36">
         <v>0.3087982760018804</v>
       </c>
       <c r="F36">
-        <v>0.4489832632463832</v>
+        <v>0.2743085116504074</v>
       </c>
       <c r="G36">
-        <v>-0.1401849872445028</v>
+        <v>0.034489764351473</v>
       </c>
       <c r="H36">
-        <v>0.1401849872445028</v>
+        <v>-0.034489764351473</v>
       </c>
       <c r="I36">
-        <v>0.1062295954136375</v>
+        <v>-0.0201112156978718</v>
       </c>
       <c r="J36" t="b">
         <v>1</v>
       </c>
       <c r="K36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
